--- a/backend/sample_data/05_Semester_Marks_and_Grades.xlsx
+++ b/backend/sample_data/05_Semester_Marks_and_Grades.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,11 +449,21 @@
           <t>external_score</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>semester</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>academic_year</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SU2026-0015</t>
+          <t>SU2026-0001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,11 +477,19 @@
       <c r="D2" t="n">
         <v>64</v>
       </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SU2026-0015</t>
+          <t>SU2026-0001</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -485,11 +503,19 @@
       <c r="D3" t="n">
         <v>58.5</v>
       </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SU2026-0015</t>
+          <t>SU2026-0001</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -503,11 +529,19 @@
       <c r="D4" t="n">
         <v>60</v>
       </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SU2026-0016</t>
+          <t>SU2026-0002</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -521,11 +555,19 @@
       <c r="D5" t="n">
         <v>52</v>
       </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SU2026-0016</t>
+          <t>SU2026-0002</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -539,11 +581,19 @@
       <c r="D6" t="n">
         <v>48</v>
       </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SU2026-0016</t>
+          <t>SU2026-0002</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -557,11 +607,19 @@
       <c r="D7" t="n">
         <v>55</v>
       </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SU2026-0017</t>
+          <t>SU2026-0003</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -575,11 +633,19 @@
       <c r="D8" t="n">
         <v>42</v>
       </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SU2026-0017</t>
+          <t>SU2026-0003</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -593,11 +659,19 @@
       <c r="D9" t="n">
         <v>38</v>
       </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SU2026-0017</t>
+          <t>SU2026-0003</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -610,6 +684,14 @@
       </c>
       <c r="D10" t="n">
         <v>45</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
       </c>
     </row>
   </sheetData>
